--- a/artifacts/produtos_entrada_template.xlsx
+++ b/artifacts/produtos_entrada_template.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produtos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$3:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$3:$E$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Produtos'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -206,12 +206,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TabelaProdutos" displayName="TabelaProdutos" ref="A3:C7" headerRowCount="1">
-  <autoFilter ref="A3:C7"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Nome do produto"/>
-    <tableColumn id="2" name="ID do produto"/>
-    <tableColumn id="3" name="Link do produto"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TabelaProdutos" displayName="TabelaProdutos" ref="A3:E7" headerRowCount="1">
+  <autoFilter ref="A3:E7"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Grupo"/>
+    <tableColumn id="2" name="Nome do produto"/>
+    <tableColumn id="3" name="ID do produto"/>
+    <tableColumn id="4" name="Link do produto"/>
+    <tableColumn id="5" name="CEPs para testar"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -506,114 +508,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="18" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="18" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Template de Produtos</t>
+          <t>Template de Produtos (Grupos + CEPs)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Preencha Nome e Link. O ID é para controle interno (não usar em pesquisas).</t>
+          <t>Preencha Link. Opcional: Grupo e CEPs (se vazio, usa o CEP padrão informado na UI). O ID é para controle interno.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
           <t>Nome do produto</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>ID do produto</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Link do produto</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>CEPs para testar</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
+          <t>Grupo A (Exemplo)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
           <t>Colchão Casal Premium (Exemplo)</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>PRD-000001</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>https://exemplo.com.br/produtos/colchao-casal-premium</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>01001-000, 20040-002</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
+          <t>Grupo A (Exemplo)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
           <t>Travesseiro Ortopédico (Exemplo)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>PRD-000002</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>https://exemplo.com.br/produtos/travesseiro-ortopedico</t>
         </is>
       </c>
+      <c r="E5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
+          <t>Grupo B (Exemplo)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
           <t>Cama Box Solteiro (Exemplo)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>PRD-000003</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>https://exemplo.com.br/produtos/cama-box-solteiro</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>79800-002</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
+          <t>Grupo B (Exemplo)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
           <t>Protetor de Colchão Queen (Exemplo)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>PRD-000004</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>https://exemplo.com.br/produtos/protetor-colchao-queen</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>04094-050; 30110-012</t>
         </is>
       </c>
     </row>
@@ -621,251 +675,332 @@
       <c r="A8" s="6" t="inlineStr"/>
       <c r="B8" s="6" t="inlineStr"/>
       <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr"/>
       <c r="B9" s="6" t="inlineStr"/>
       <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr"/>
       <c r="B11" s="6" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr"/>
       <c r="B13" s="6" t="inlineStr"/>
       <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
       <c r="B14" s="6" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr"/>
       <c r="B15" s="6" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr"/>
       <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr"/>
       <c r="B17" s="6" t="inlineStr"/>
       <c r="C17" s="6" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr"/>
       <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr"/>
       <c r="B19" s="6" t="inlineStr"/>
       <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr"/>
       <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr"/>
       <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr"/>
       <c r="C23" s="6" t="inlineStr"/>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr"/>
       <c r="C24" s="6" t="inlineStr"/>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr"/>
       <c r="C25" s="6" t="inlineStr"/>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr"/>
       <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr"/>
       <c r="B27" s="6" t="inlineStr"/>
       <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr"/>
       <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr"/>
       <c r="B29" s="6" t="inlineStr"/>
       <c r="C29" s="6" t="inlineStr"/>
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr"/>
       <c r="C30" s="6" t="inlineStr"/>
+      <c r="D30" s="6" t="inlineStr"/>
+      <c r="E30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr"/>
       <c r="B31" s="6" t="inlineStr"/>
       <c r="C31" s="6" t="inlineStr"/>
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr"/>
       <c r="C32" s="6" t="inlineStr"/>
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr"/>
       <c r="C33" s="6" t="inlineStr"/>
+      <c r="D33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr"/>
       <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr"/>
       <c r="C35" s="6" t="inlineStr"/>
+      <c r="D35" s="6" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr"/>
       <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr"/>
       <c r="B37" s="6" t="inlineStr"/>
       <c r="C37" s="6" t="inlineStr"/>
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr"/>
       <c r="C38" s="6" t="inlineStr"/>
+      <c r="D38" s="6" t="inlineStr"/>
+      <c r="E38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr"/>
       <c r="B39" s="6" t="inlineStr"/>
       <c r="C39" s="6" t="inlineStr"/>
+      <c r="D39" s="6" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr"/>
       <c r="C40" s="6" t="inlineStr"/>
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr"/>
       <c r="B41" s="6" t="inlineStr"/>
       <c r="C41" s="6" t="inlineStr"/>
+      <c r="D41" s="6" t="inlineStr"/>
+      <c r="E41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr"/>
       <c r="B42" s="6" t="inlineStr"/>
       <c r="C42" s="6" t="inlineStr"/>
+      <c r="D42" s="6" t="inlineStr"/>
+      <c r="E42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr"/>
       <c r="B43" s="6" t="inlineStr"/>
       <c r="C43" s="6" t="inlineStr"/>
+      <c r="D43" s="6" t="inlineStr"/>
+      <c r="E43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr"/>
       <c r="B44" s="6" t="inlineStr"/>
       <c r="C44" s="6" t="inlineStr"/>
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr"/>
       <c r="B45" s="6" t="inlineStr"/>
       <c r="C45" s="6" t="inlineStr"/>
+      <c r="D45" s="6" t="inlineStr"/>
+      <c r="E45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr"/>
       <c r="B46" s="6" t="inlineStr"/>
       <c r="C46" s="6" t="inlineStr"/>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr"/>
       <c r="B47" s="6" t="inlineStr"/>
       <c r="C47" s="6" t="inlineStr"/>
+      <c r="D47" s="6" t="inlineStr"/>
+      <c r="E47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr"/>
       <c r="B48" s="6" t="inlineStr"/>
       <c r="C48" s="6" t="inlineStr"/>
+      <c r="D48" s="6" t="inlineStr"/>
+      <c r="E48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr"/>
       <c r="B49" s="6" t="inlineStr"/>
       <c r="C49" s="6" t="inlineStr"/>
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr"/>
       <c r="B50" s="6" t="inlineStr"/>
       <c r="C50" s="6" t="inlineStr"/>
+      <c r="D50" s="6" t="inlineStr"/>
+      <c r="E50" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C7"/>
+  <autoFilter ref="A3:E7"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A4:A1000">
+  <conditionalFormatting sqref="D4:D1000">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>LEN(TRIM(A4))=0</formula>
+      <formula>LEN(TRIM(D4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C1000">
-    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
-      <formula>LEN(TRIM(C4))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B1000">
-    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="0">
-      <formula>AND(LEN(TRIM(B4))&gt;0,NOT(AND(LEN(B4)=10,LEFT(B4,4)="PRD-",ISNUMBER(VALUE(RIGHT(B4,6))))))</formula>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>AND(LEN(TRIM(C4))&gt;0,NOT(AND(LEN(C4)=10,LEFT(C4,4)="PRD-",ISNUMBER(VALUE(RIGHT(C4,6))))))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B4:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="ID inválido" error="Use o formato PRD-000001 (PRD- + 6 dígitos)." type="custom">
-      <formula1>=AND(LEN(B4)=10,LEFT(B4,4)="PRD-",ISNUMBER(VALUE(RIGHT(B4,6))))</formula1>
+    <dataValidation sqref="C4:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="ID inválido" error="Use o formato PRD-000001 (PRD- + 6 dígitos)." type="custom">
+      <formula1>=AND(LEN(C4)=10,LEFT(C4,4)="PRD-",ISNUMBER(VALUE(RIGHT(C4,6))))</formula1>
     </dataValidation>
-    <dataValidation sqref="C4:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Link inválido" error="Informe um link começando com http:// ou https://" type="custom">
-      <formula1>=OR(LEFT(C4,7)="http://",LEFT(C4,8)="https://")</formula1>
+    <dataValidation sqref="D4:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Link inválido" error="Informe um link começando com http:// ou https://" type="custom">
+      <formula1>=OR(LEFT(D4,7)="http://",LEFT(D4,8)="https://")</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
